--- a/web/public/forms/geomcheuk-budae.xlsx
+++ b/web/public/forms/geomcheuk-budae.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부대공 검측 체크리스트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'부대공 검측 체크리스트'!$A$1:$X$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'부대공 검측 체크리스트'!$A$1:$X$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,37 +36,58 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,12 +96,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F8FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,23 +125,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -114,35 +150,59 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X53"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -538,15 +598,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -570,7 +630,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -600,7 +660,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -630,7 +690,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -660,7 +720,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="7" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -690,7 +750,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -711,7 +771,7 @@
     </row>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>▣ 방음벽(방음판)</t>
         </is>
@@ -719,13 +779,13 @@
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>검사 항목</t>
         </is>
@@ -739,7 +799,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="n"/>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>검사기준</t>
         </is>
@@ -747,19 +807,19 @@
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="Q13" s="9" t="inlineStr">
         <is>
           <t>합격</t>
         </is>
       </c>
       <c r="R13" s="5" t="n"/>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="S13" s="9" t="inlineStr">
         <is>
           <t>불합격</t>
         </is>
       </c>
       <c r="T13" s="5" t="n"/>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="U13" s="9" t="inlineStr">
         <is>
           <t>조치사항</t>
         </is>
@@ -768,14 +828,14 @@
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
-    <row r="14" ht="43.5" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>기초지반의 잡석은 다져저 있는지 확인하였는가?</t>
         </is>
@@ -789,27 +849,27 @@
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="10" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="9" t="inlineStr"/>
+      <c r="Q14" s="10" t="n"/>
       <c r="R14" s="5" t="n"/>
-      <c r="S14" s="9" t="inlineStr"/>
+      <c r="S14" s="10" t="n"/>
       <c r="T14" s="5" t="n"/>
-      <c r="U14" s="9" t="inlineStr"/>
+      <c r="U14" s="10" t="n"/>
       <c r="V14" s="5" t="n"/>
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
-    <row r="15" ht="43.5" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>기초부의 폭, 연장, 선형은 도면과 일치하는가?</t>
         </is>
@@ -823,27 +883,27 @@
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="n"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="10" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="9" t="inlineStr"/>
+      <c r="Q15" s="10" t="n"/>
       <c r="R15" s="5" t="n"/>
-      <c r="S15" s="9" t="inlineStr"/>
+      <c r="S15" s="10" t="n"/>
       <c r="T15" s="5" t="n"/>
-      <c r="U15" s="9" t="inlineStr"/>
+      <c r="U15" s="10" t="n"/>
       <c r="V15" s="5" t="n"/>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>도수로 시공부위의 배수관 시설 설치위치는 도면과 일치하는가?</t>
         </is>
@@ -857,27 +917,27 @@
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="10" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="9" t="inlineStr"/>
+      <c r="Q16" s="10" t="n"/>
       <c r="R16" s="5" t="n"/>
-      <c r="S16" s="9" t="inlineStr"/>
+      <c r="S16" s="10" t="n"/>
       <c r="T16" s="5" t="n"/>
-      <c r="U16" s="9" t="inlineStr"/>
+      <c r="U16" s="10" t="n"/>
       <c r="V16" s="5" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>거푸집은 견고하고 단차나 틈, 철근조립 상태는 도면과 일치하는가?</t>
         </is>
@@ -891,27 +951,27 @@
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="10" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="9" t="inlineStr"/>
+      <c r="Q17" s="10" t="n"/>
       <c r="R17" s="5" t="n"/>
-      <c r="S17" s="9" t="inlineStr"/>
+      <c r="S17" s="10" t="n"/>
       <c r="T17" s="5" t="n"/>
-      <c r="U17" s="9" t="inlineStr"/>
+      <c r="U17" s="10" t="n"/>
       <c r="V17" s="5" t="n"/>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>지주간격이 방음판 규격에 맞추어 일정간격이 유지되도록 배치되었는가?</t>
         </is>
@@ -925,27 +985,27 @@
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="M18" s="10" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="9" t="inlineStr"/>
+      <c r="Q18" s="10" t="n"/>
       <c r="R18" s="5" t="n"/>
-      <c r="S18" s="9" t="inlineStr"/>
+      <c r="S18" s="10" t="n"/>
       <c r="T18" s="5" t="n"/>
-      <c r="U18" s="9" t="inlineStr"/>
+      <c r="U18" s="10" t="n"/>
       <c r="V18" s="5" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
-    <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>지주의 높이가 도면대로 시공되었는가?</t>
         </is>
@@ -959,27 +1019,27 @@
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="n"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="10" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="9" t="inlineStr"/>
+      <c r="Q19" s="10" t="n"/>
       <c r="R19" s="5" t="n"/>
-      <c r="S19" s="9" t="inlineStr"/>
+      <c r="S19" s="10" t="n"/>
       <c r="T19" s="5" t="n"/>
-      <c r="U19" s="9" t="inlineStr"/>
+      <c r="U19" s="10" t="n"/>
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>방음벽 구체 콘크리트의 상단면은 틈새가 생기지 않도록 평활하게 마무리되었는가?</t>
         </is>
@@ -993,27 +1053,27 @@
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="10" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="9" t="inlineStr"/>
+      <c r="Q20" s="10" t="n"/>
       <c r="R20" s="5" t="n"/>
-      <c r="S20" s="9" t="inlineStr"/>
+      <c r="S20" s="10" t="n"/>
       <c r="T20" s="5" t="n"/>
-      <c r="U20" s="9" t="inlineStr"/>
+      <c r="U20" s="10" t="n"/>
       <c r="V20" s="5" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
-    <row r="21" ht="43.5" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>콘크리트 타설면의 미관은 양호하며 선형은 도면과 일치하는가?</t>
         </is>
@@ -1027,27 +1087,27 @@
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="n"/>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="10" t="n"/>
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="9" t="inlineStr"/>
+      <c r="Q21" s="10" t="n"/>
       <c r="R21" s="5" t="n"/>
-      <c r="S21" s="9" t="inlineStr"/>
+      <c r="S21" s="10" t="n"/>
       <c r="T21" s="5" t="n"/>
-      <c r="U21" s="9" t="inlineStr"/>
+      <c r="U21" s="10" t="n"/>
       <c r="V21" s="5" t="n"/>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
-    <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>방음판 하단부 틈새 발생은 없는가?</t>
         </is>
@@ -1061,27 +1121,27 @@
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="n"/>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="M22" s="10" t="n"/>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="9" t="inlineStr"/>
+      <c r="Q22" s="10" t="n"/>
       <c r="R22" s="5" t="n"/>
-      <c r="S22" s="9" t="inlineStr"/>
+      <c r="S22" s="10" t="n"/>
       <c r="T22" s="5" t="n"/>
-      <c r="U22" s="9" t="inlineStr"/>
+      <c r="U22" s="10" t="n"/>
       <c r="V22" s="5" t="n"/>
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
-    <row r="23" ht="43.5" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="B23" s="5" t="n"/>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>방음판의 재질 및 구조가 시방기준에 적합한가?</t>
         </is>
@@ -1095,27 +1155,27 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="5" t="n"/>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="M23" s="10" t="n"/>
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="9" t="inlineStr"/>
+      <c r="Q23" s="10" t="n"/>
       <c r="R23" s="5" t="n"/>
-      <c r="S23" s="9" t="inlineStr"/>
+      <c r="S23" s="10" t="n"/>
       <c r="T23" s="5" t="n"/>
-      <c r="U23" s="9" t="inlineStr"/>
+      <c r="U23" s="10" t="n"/>
       <c r="V23" s="5" t="n"/>
       <c r="W23" s="5" t="n"/>
       <c r="X23" s="5" t="n"/>
     </row>
-    <row r="24" ht="43.5" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>운반 및 보관중 손상된 것을 설치하지 않는가?</t>
         </is>
@@ -1129,27 +1189,27 @@
       <c r="J24" s="5" t="n"/>
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="n"/>
-      <c r="M24" s="9" t="inlineStr"/>
+      <c r="M24" s="10" t="n"/>
       <c r="N24" s="5" t="n"/>
       <c r="O24" s="5" t="n"/>
       <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="9" t="inlineStr"/>
+      <c r="Q24" s="10" t="n"/>
       <c r="R24" s="5" t="n"/>
-      <c r="S24" s="9" t="inlineStr"/>
+      <c r="S24" s="10" t="n"/>
       <c r="T24" s="5" t="n"/>
-      <c r="U24" s="9" t="inlineStr"/>
+      <c r="U24" s="10" t="n"/>
       <c r="V24" s="5" t="n"/>
       <c r="W24" s="5" t="n"/>
       <c r="X24" s="5" t="n"/>
     </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>방음판에 내장된 흡음재의 열화 및 처짐방지용 보호피막이 도포되어 있는가?</t>
         </is>
@@ -1163,27 +1223,27 @@
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
-      <c r="M25" s="9" t="inlineStr"/>
+      <c r="M25" s="10" t="n"/>
       <c r="N25" s="5" t="n"/>
       <c r="O25" s="5" t="n"/>
       <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="9" t="inlineStr"/>
+      <c r="Q25" s="10" t="n"/>
       <c r="R25" s="5" t="n"/>
-      <c r="S25" s="9" t="inlineStr"/>
+      <c r="S25" s="10" t="n"/>
       <c r="T25" s="5" t="n"/>
-      <c r="U25" s="9" t="inlineStr"/>
+      <c r="U25" s="10" t="n"/>
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>설치기준에 부합되는가?</t>
         </is>
@@ -1197,27 +1257,27 @@
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="5" t="n"/>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="10" t="n"/>
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="5" t="n"/>
       <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="9" t="inlineStr"/>
+      <c r="Q26" s="10" t="n"/>
       <c r="R26" s="5" t="n"/>
-      <c r="S26" s="9" t="inlineStr"/>
+      <c r="S26" s="10" t="n"/>
       <c r="T26" s="5" t="n"/>
-      <c r="U26" s="9" t="inlineStr"/>
+      <c r="U26" s="10" t="n"/>
       <c r="V26" s="5" t="n"/>
       <c r="W26" s="5" t="n"/>
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>선정기준에 부합되는가?</t>
         </is>
@@ -1231,634 +1291,2391 @@
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="5" t="n"/>
       <c r="L27" s="5" t="n"/>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="M27" s="10" t="n"/>
       <c r="N27" s="5" t="n"/>
       <c r="O27" s="5" t="n"/>
       <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="9" t="inlineStr"/>
+      <c r="Q27" s="10" t="n"/>
       <c r="R27" s="5" t="n"/>
-      <c r="S27" s="9" t="inlineStr"/>
+      <c r="S27" s="10" t="n"/>
       <c r="T27" s="5" t="n"/>
-      <c r="U27" s="9" t="inlineStr"/>
+      <c r="U27" s="10" t="n"/>
       <c r="V27" s="5" t="n"/>
       <c r="W27" s="5" t="n"/>
       <c r="X27" s="5" t="n"/>
     </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="13">
+        <f>IF(COUNTA(Q14:Q27,S14:S27)=0,"","합격 "&amp;COUNTA(Q14:Q27)&amp;" · 불합격 "&amp;COUNTA(S14:S27))</f>
+        <v/>
+      </c>
+      <c r="V28" s="5" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30" ht="7.666666666666667" customHeight="1"/>
+    <row r="31" ht="7.666666666666667" customHeight="1"/>
+    <row r="32" ht="7.666666666666667" customHeight="1"/>
+    <row r="33" ht="7.666666666666667" customHeight="1"/>
+    <row r="34" ht="7.666666666666667" customHeight="1"/>
+    <row r="35" ht="7.666666666666667" customHeight="1"/>
+    <row r="36" ht="7.666666666666667" customHeight="1"/>
+    <row r="37" ht="7.666666666666667" customHeight="1"/>
+    <row r="38" ht="7.666666666666667" customHeight="1"/>
+    <row r="39" ht="7.666666666666667" customHeight="1"/>
+    <row r="40" ht="7.666666666666667" customHeight="1"/>
+    <row r="41" ht="7.666666666666667" customHeight="1"/>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>▣ 방음벽(기초)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>검사 항목</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="8" t="inlineStr">
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="9" t="inlineStr">
         <is>
           <t>검사기준</t>
         </is>
       </c>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="8" t="inlineStr">
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
+      <c r="Q44" s="9" t="inlineStr">
         <is>
           <t>합격</t>
         </is>
       </c>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="8" t="inlineStr">
+      <c r="R44" s="5" t="n"/>
+      <c r="S44" s="9" t="inlineStr">
         <is>
           <t>불합격</t>
         </is>
       </c>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="8" t="inlineStr">
+      <c r="T44" s="5" t="n"/>
+      <c r="U44" s="9" t="inlineStr">
         <is>
           <t>조치사항</t>
         </is>
       </c>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="43.5" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="V44" s="5" t="n"/>
+      <c r="W44" s="5" t="n"/>
+      <c r="X44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>기초의 폭,연장, 선형 및 지지력은 확인하였는가?</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="9" t="inlineStr"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="9" t="inlineStr"/>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="9" t="inlineStr"/>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="9" t="inlineStr"/>
-      <c r="V32" s="5" t="n"/>
-      <c r="W32" s="5" t="n"/>
-      <c r="X32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="43.5" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="5" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="5" t="n"/>
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="5" t="n"/>
+      <c r="W45" s="5" t="n"/>
+      <c r="X45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>도수로 시공부위의 배수관, 집수정 시설 설치위치는 적정한가?</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="9" t="inlineStr"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="9" t="inlineStr"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="9" t="inlineStr"/>
-      <c r="T33" s="5" t="n"/>
-      <c r="U33" s="9" t="inlineStr"/>
-      <c r="V33" s="5" t="n"/>
-      <c r="W33" s="5" t="n"/>
-      <c r="X33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="43.5" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="5" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="5" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="5" t="n"/>
+      <c r="W46" s="5" t="n"/>
+      <c r="X46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>거푸집 설치 및 철근조립 상태는 양호한가?</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="9" t="inlineStr"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="9" t="inlineStr"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="9" t="inlineStr"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="9" t="inlineStr"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="6" customHeight="1"/>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="5" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="5" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="5" t="n"/>
+      <c r="W47" s="5" t="n"/>
+      <c r="X47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
+      <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n"/>
+      <c r="T48" s="5" t="n"/>
+      <c r="U48" s="13">
+        <f>IF(COUNTA(Q45:Q47,S45:S47)=0,"","합격 "&amp;COUNTA(Q45:Q47)&amp;" · 불합격 "&amp;COUNTA(S45:S47))</f>
+        <v/>
+      </c>
+      <c r="V48" s="5" t="n"/>
+      <c r="W48" s="5" t="n"/>
+      <c r="X48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="6" customHeight="1"/>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>▣ 방음벽(구체)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="51" ht="6" customHeight="1"/>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>검사 항목</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="8" t="inlineStr">
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>검사기준</t>
         </is>
       </c>
-      <c r="N38" s="5" t="n"/>
-      <c r="O38" s="5" t="n"/>
-      <c r="P38" s="5" t="n"/>
-      <c r="Q38" s="8" t="inlineStr">
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
+      <c r="Q52" s="9" t="inlineStr">
         <is>
           <t>합격</t>
         </is>
       </c>
-      <c r="R38" s="5" t="n"/>
-      <c r="S38" s="8" t="inlineStr">
+      <c r="R52" s="5" t="n"/>
+      <c r="S52" s="9" t="inlineStr">
         <is>
           <t>불합격</t>
         </is>
       </c>
-      <c r="T38" s="5" t="n"/>
-      <c r="U38" s="8" t="inlineStr">
+      <c r="T52" s="5" t="n"/>
+      <c r="U52" s="9" t="inlineStr">
         <is>
           <t>조치사항</t>
         </is>
       </c>
-      <c r="V38" s="5" t="n"/>
-      <c r="W38" s="5" t="n"/>
-      <c r="X38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="V52" s="5" t="n"/>
+      <c r="W52" s="5" t="n"/>
+      <c r="X52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>지주간격이 방음판 규격에 맟추어 일정간격이 유지되도록 배치되었는가?</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="9" t="inlineStr"/>
-      <c r="N39" s="5" t="n"/>
-      <c r="O39" s="5" t="n"/>
-      <c r="P39" s="5" t="n"/>
-      <c r="Q39" s="9" t="inlineStr"/>
-      <c r="R39" s="5" t="n"/>
-      <c r="S39" s="9" t="inlineStr"/>
-      <c r="T39" s="5" t="n"/>
-      <c r="U39" s="9" t="inlineStr"/>
-      <c r="V39" s="5" t="n"/>
-      <c r="W39" s="5" t="n"/>
-      <c r="X39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="43.5" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="5" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="5" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="5" t="n"/>
+      <c r="W53" s="5" t="n"/>
+      <c r="X53" s="5" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>지주의 높이가 설계대로 시공되었는가?</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="9" t="inlineStr"/>
-      <c r="N40" s="5" t="n"/>
-      <c r="O40" s="5" t="n"/>
-      <c r="P40" s="5" t="n"/>
-      <c r="Q40" s="9" t="inlineStr"/>
-      <c r="R40" s="5" t="n"/>
-      <c r="S40" s="9" t="inlineStr"/>
-      <c r="T40" s="5" t="n"/>
-      <c r="U40" s="9" t="inlineStr"/>
-      <c r="V40" s="5" t="n"/>
-      <c r="W40" s="5" t="n"/>
-      <c r="X40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="5" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="5" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="5" t="n"/>
+      <c r="W54" s="5" t="n"/>
+      <c r="X54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>방음벽 구체 콘크리트의 상단면은 틈새가 생기지 않도록 평활하게 마무리 되었는가?</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="9" t="inlineStr"/>
-      <c r="N41" s="5" t="n"/>
-      <c r="O41" s="5" t="n"/>
-      <c r="P41" s="5" t="n"/>
-      <c r="Q41" s="9" t="inlineStr"/>
-      <c r="R41" s="5" t="n"/>
-      <c r="S41" s="9" t="inlineStr"/>
-      <c r="T41" s="5" t="n"/>
-      <c r="U41" s="9" t="inlineStr"/>
-      <c r="V41" s="5" t="n"/>
-      <c r="W41" s="5" t="n"/>
-      <c r="X41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="43.5" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="5" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="5" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="5" t="n"/>
+      <c r="W55" s="5" t="n"/>
+      <c r="X55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>거푸집 설치및철근 조립상태는 양호한가?</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="9" t="inlineStr"/>
-      <c r="N42" s="5" t="n"/>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="5" t="n"/>
-      <c r="Q42" s="9" t="inlineStr"/>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="9" t="inlineStr"/>
-      <c r="T42" s="5" t="n"/>
-      <c r="U42" s="9" t="inlineStr"/>
-      <c r="V42" s="5" t="n"/>
-      <c r="W42" s="5" t="n"/>
-      <c r="X42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="43.5" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="5" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="5" t="n"/>
+      <c r="W56" s="5" t="n"/>
+      <c r="X56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>콘크리트 타설면의 미관 및 선형은 양호한가?</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="9" t="inlineStr"/>
-      <c r="N43" s="5" t="n"/>
-      <c r="O43" s="5" t="n"/>
-      <c r="P43" s="5" t="n"/>
-      <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="5" t="n"/>
-      <c r="S43" s="9" t="inlineStr"/>
-      <c r="T43" s="5" t="n"/>
-      <c r="U43" s="9" t="inlineStr"/>
-      <c r="V43" s="5" t="n"/>
-      <c r="W43" s="5" t="n"/>
-      <c r="X43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="45" ht="10" customHeight="1"/>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="K47" s="11" t="inlineStr">
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="5" t="n"/>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
+      <c r="U58" s="13">
+        <f>IF(COUNTA(Q53:Q57,S53:S57)=0,"","합격 "&amp;COUNTA(Q53:Q57)&amp;" · 불합격 "&amp;COUNTA(S53:S57))</f>
+        <v/>
+      </c>
+      <c r="V58" s="5" t="n"/>
+      <c r="W58" s="5" t="n"/>
+      <c r="X58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="6" customHeight="1"/>
+    <row r="60" ht="10" customHeight="1"/>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="15" t="inlineStr"/>
+      <c r="K62" s="16" t="inlineStr">
         <is>
           <t>시공자 점검직원</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="Q62" s="17" t="n"/>
+      <c r="U62" s="18" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="K48" s="11" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="15" t="inlineStr"/>
+      <c r="K63" s="16" t="inlineStr">
         <is>
           <t>검측 감리원</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="Q63" s="17" t="n"/>
+      <c r="U63" s="18" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>※ 검사·시험값이 있으면 값을 적고, 합격은 A · 불합격은 UA 로 표기합니다.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="53">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="65" ht="6" customHeight="1"/>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>합격 칸·불합격 칸을 누르면 목록(A · UA)이 나옵니다. 표마다 맨 아래에 합격·불합격 개수가 저절로 셉니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="173">
+  <mergeCells count="185">
     <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="U52:X52"/>
+    <mergeCell ref="A69:X69"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="Q21:R21"/>
     <mergeCell ref="C23:L23"/>
+    <mergeCell ref="A58:T58"/>
     <mergeCell ref="S21:T21"/>
-    <mergeCell ref="U39:X39"/>
-    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="U54:X54"/>
+    <mergeCell ref="M57:P57"/>
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="U23:X23"/>
-    <mergeCell ref="U38:X38"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="C57:L57"/>
     <mergeCell ref="A3:X3"/>
+    <mergeCell ref="M46:P46"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="Q55:R55"/>
+    <mergeCell ref="M56:P56"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="U31:X31"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="U40:X40"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="K47:R47"/>
-    <mergeCell ref="C34:L34"/>
     <mergeCell ref="U15:X15"/>
     <mergeCell ref="Q26:R26"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C42:L42"/>
-    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="S57:T57"/>
+    <mergeCell ref="Q62:T62"/>
     <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="K62:P62"/>
     <mergeCell ref="C20:L20"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M54:P54"/>
     <mergeCell ref="Q27:R27"/>
     <mergeCell ref="U16:X16"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="U25:X25"/>
+    <mergeCell ref="A67:X67"/>
+    <mergeCell ref="Q63:T63"/>
     <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="U57:X57"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="M16:P16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="S20:T20"/>
     <mergeCell ref="M25:P25"/>
+    <mergeCell ref="C46:L46"/>
+    <mergeCell ref="A28:T28"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="M18:P18"/>
-    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="U28:X28"/>
     <mergeCell ref="S22:T22"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="M45:P45"/>
+    <mergeCell ref="Q53:R53"/>
+    <mergeCell ref="S47:T47"/>
     <mergeCell ref="G7:X7"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="M17:P17"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="C38:L38"/>
+    <mergeCell ref="A48:T48"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="S46:T46"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="Q52:R52"/>
     <mergeCell ref="U20:X20"/>
+    <mergeCell ref="S52:T52"/>
     <mergeCell ref="U14:X14"/>
-    <mergeCell ref="Q39:R39"/>
     <mergeCell ref="M19:P19"/>
-    <mergeCell ref="S39:T39"/>
     <mergeCell ref="C13:L13"/>
+    <mergeCell ref="Q54:R54"/>
+    <mergeCell ref="A50:X50"/>
     <mergeCell ref="Q23:R23"/>
     <mergeCell ref="U22:X22"/>
-    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="A42:X42"/>
     <mergeCell ref="S23:T23"/>
-    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="C15:L15"/>
     <mergeCell ref="S13:T13"/>
     <mergeCell ref="C24:L24"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="M44:P44"/>
+    <mergeCell ref="U46:X46"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
     <mergeCell ref="Q15:R15"/>
     <mergeCell ref="S15:T15"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="S24:T24"/>
-    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="U48:X48"/>
     <mergeCell ref="G9:X9"/>
     <mergeCell ref="C16:L16"/>
     <mergeCell ref="C25:L25"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="C55:L55"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="M13:P13"/>
+    <mergeCell ref="U47:X47"/>
+    <mergeCell ref="A64:X64"/>
     <mergeCell ref="M21:P21"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="S48:X48"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="U56:X56"/>
+    <mergeCell ref="Q57:R57"/>
+    <mergeCell ref="A61:X61"/>
     <mergeCell ref="U24:X24"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="U18:X18"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="U58:X58"/>
+    <mergeCell ref="K63:P63"/>
+    <mergeCell ref="C52:L52"/>
+    <mergeCell ref="A62:J62"/>
     <mergeCell ref="U19:X19"/>
+    <mergeCell ref="M53:P53"/>
+    <mergeCell ref="U44:X44"/>
     <mergeCell ref="Q20:R20"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="M34:P34"/>
     <mergeCell ref="S14:T14"/>
+    <mergeCell ref="M55:P55"/>
     <mergeCell ref="C14:L14"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M39:P39"/>
-    <mergeCell ref="A53:X53"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="U45:X45"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="Q46:R46"/>
+    <mergeCell ref="A68:X68"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C41:L41"/>
-    <mergeCell ref="S47:X47"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="M40:P40"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C54:L54"/>
+    <mergeCell ref="S55:T55"/>
+    <mergeCell ref="Q45:R45"/>
     <mergeCell ref="U13:X13"/>
-    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="C56:L56"/>
+    <mergeCell ref="S54:T54"/>
     <mergeCell ref="A11:X11"/>
     <mergeCell ref="U21:X21"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="Q41:R41"/>
     <mergeCell ref="S26:T26"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="C43:L43"/>
+    <mergeCell ref="Q47:R47"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="U62:X62"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q56:R56"/>
+    <mergeCell ref="S56:T56"/>
     <mergeCell ref="S25:T25"/>
     <mergeCell ref="M26:P26"/>
-    <mergeCell ref="M41:P41"/>
-    <mergeCell ref="Q43:R43"/>
-    <mergeCell ref="S43:T43"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="U55:X55"/>
     <mergeCell ref="Q24:R24"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q33:R33"/>
     <mergeCell ref="S18:T18"/>
     <mergeCell ref="S27:T27"/>
-    <mergeCell ref="M38:P38"/>
-    <mergeCell ref="A46:X46"/>
     <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S44:T44"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="S17:T17"/>
     <mergeCell ref="U26:X26"/>
+    <mergeCell ref="C53:L53"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="U63:X63"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="U34:X34"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="M52:P52"/>
+    <mergeCell ref="C45:L45"/>
     <mergeCell ref="U27:X27"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="Q44:R44"/>
     <mergeCell ref="U17:X17"/>
     <mergeCell ref="M20:P20"/>
     <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="C47:L47"/>
+    <mergeCell ref="S45:T45"/>
+    <mergeCell ref="C44:L44"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C31:L31"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="U53:X53"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C21:L21"/>
-    <mergeCell ref="A49:X49"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="M15:P15"/>
-    <mergeCell ref="A36:X36"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="S31:T31"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <dataValidations count="2">
+    <dataValidation sqref="Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q45 Q46 Q47 Q53 Q54 Q55 Q56 Q57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S45 S46 S47 S53 S54 S55 S56 S57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"UA"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>검 측 체 크 리 스 트  (부대공)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공        종</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>부대공 — 방음벽</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  위치 및 부위</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>STA.0+500 ~ 0+560 좌측</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  검 측 일 자</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공  사  량</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>L=60m</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>▣ 방음벽(방음판)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>검사 항목</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>검사기준</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>불합격</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="9" t="inlineStr">
+        <is>
+          <t>조치사항</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>기초지반의 잡석은 다져저 있는지 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>기초부의 폭, 연장, 선형은 도면과 일치하는가?</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>도수로 시공부위의 배수관 시설 설치위치는 도면과 일치하는가?</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>거푸집은 견고하고 단차나 틈, 철근조립 상태는 도면과 일치하는가?</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>지주간격이 방음판 규격에 맞추어 일정간격이 유지되도록 배치되었는가?</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>지주의 높이가 도면대로 시공되었는가?</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>방음벽 구체 콘크리트의 상단면은 틈새가 생기지 않도록 평활하게 마무리되었는가?</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="10" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>콘크리트 타설면의 미관은 양호하며 선형은 도면과 일치하는가?</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>방음판 하단부 틈새 발생은 없는가?</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="10" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="10" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>방음판의 재질 및 구조가 시방기준에 적합한가?</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="10" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="10" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>운반 및 보관중 손상된 것을 설치하지 않는가?</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="10" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="10" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>방음판에 내장된 흡음재의 열화 및 처짐방지용 보호피막이 도포되어 있는가?</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="10" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="10" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>설치기준에 부합되는가?</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="10" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="10" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>선정기준에 부합되는가?</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="10" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="10" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="13">
+        <f>IF(COUNTA(Q14:Q27,S14:S27)=0,"","합격 "&amp;COUNTA(Q14:Q27)&amp;" · 불합격 "&amp;COUNTA(S14:S27))</f>
+        <v/>
+      </c>
+      <c r="V28" s="5" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30" ht="7.666666666666667" customHeight="1"/>
+    <row r="31" ht="7.666666666666667" customHeight="1"/>
+    <row r="32" ht="7.666666666666667" customHeight="1"/>
+    <row r="33" ht="7.666666666666667" customHeight="1"/>
+    <row r="34" ht="7.666666666666667" customHeight="1"/>
+    <row r="35" ht="7.666666666666667" customHeight="1"/>
+    <row r="36" ht="7.666666666666667" customHeight="1"/>
+    <row r="37" ht="7.666666666666667" customHeight="1"/>
+    <row r="38" ht="7.666666666666667" customHeight="1"/>
+    <row r="39" ht="7.666666666666667" customHeight="1"/>
+    <row r="40" ht="7.666666666666667" customHeight="1"/>
+    <row r="41" ht="7.666666666666667" customHeight="1"/>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>▣ 방음벽(기초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>검사 항목</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="9" t="inlineStr">
+        <is>
+          <t>검사기준</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
+      <c r="Q44" s="9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="n"/>
+      <c r="S44" s="9" t="inlineStr">
+        <is>
+          <t>불합격</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="n"/>
+      <c r="U44" s="9" t="inlineStr">
+        <is>
+          <t>조치사항</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="n"/>
+      <c r="W44" s="5" t="n"/>
+      <c r="X44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>기초의 폭,연장, 선형 및 지지력은 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="5" t="n"/>
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="5" t="n"/>
+      <c r="W45" s="5" t="n"/>
+      <c r="X45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>도수로 시공부위의 배수관, 집수정 시설 설치위치는 적정한가?</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="5" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="5" t="n"/>
+      <c r="W46" s="5" t="n"/>
+      <c r="X46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>거푸집 설치 및 철근조립 상태는 양호한가?</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="5" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="5" t="n"/>
+      <c r="W47" s="5" t="n"/>
+      <c r="X47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
+      <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n"/>
+      <c r="T48" s="5" t="n"/>
+      <c r="U48" s="13">
+        <f>IF(COUNTA(Q45:Q47,S45:S47)=0,"","합격 "&amp;COUNTA(Q45:Q47)&amp;" · 불합격 "&amp;COUNTA(S45:S47))</f>
+        <v/>
+      </c>
+      <c r="V48" s="5" t="n"/>
+      <c r="W48" s="5" t="n"/>
+      <c r="X48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="6" customHeight="1"/>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>▣ 방음벽(구체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1"/>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>검사 항목</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="9" t="inlineStr">
+        <is>
+          <t>검사기준</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
+      <c r="Q52" s="9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="n"/>
+      <c r="S52" s="9" t="inlineStr">
+        <is>
+          <t>불합격</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="n"/>
+      <c r="U52" s="9" t="inlineStr">
+        <is>
+          <t>조치사항</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="n"/>
+      <c r="W52" s="5" t="n"/>
+      <c r="X52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>지주간격이 방음판 규격에 맟추어 일정간격이 유지되도록 배치되었는가?</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
+      <c r="Q53" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="5" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="5" t="n"/>
+      <c r="W53" s="5" t="n"/>
+      <c r="X53" s="5" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>지주의 높이가 설계대로 시공되었는가?</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
+      <c r="Q54" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="5" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="5" t="n"/>
+      <c r="W54" s="5" t="n"/>
+      <c r="X54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>방음벽 구체 콘크리트의 상단면은 틈새가 생기지 않도록 평활하게 마무리 되었는가?</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
+      <c r="Q55" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="5" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="5" t="n"/>
+      <c r="W55" s="5" t="n"/>
+      <c r="X55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>거푸집 설치및철근 조립상태는 양호한가?</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
+      <c r="Q56" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="5" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="5" t="n"/>
+      <c r="W56" s="5" t="n"/>
+      <c r="X56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>콘크리트 타설면의 미관 및 선형은 양호한가?</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="5" t="n"/>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
+      <c r="U58" s="13">
+        <f>IF(COUNTA(Q53:Q57,S53:S57)=0,"","합격 "&amp;COUNTA(Q53:Q57)&amp;" · 불합격 "&amp;COUNTA(S53:S57))</f>
+        <v/>
+      </c>
+      <c r="V58" s="5" t="n"/>
+      <c r="W58" s="5" t="n"/>
+      <c r="X58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="6" customHeight="1"/>
+    <row r="60" ht="10" customHeight="1"/>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="14" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="15" t="inlineStr"/>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
+          <t>시공자 점검직원</t>
+        </is>
+      </c>
+      <c r="Q62" s="17" t="inlineStr">
+        <is>
+          <t>이감독</t>
+        </is>
+      </c>
+      <c r="U62" s="18" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="15" t="inlineStr"/>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>검측 감리원</t>
+        </is>
+      </c>
+      <c r="Q63" s="17" t="inlineStr">
+        <is>
+          <t>박감리</t>
+        </is>
+      </c>
+      <c r="U63" s="18" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>※ 검사·시험값이 있으면 값을 적고, 합격은 A · 불합격은 UA 로 표기합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="6" customHeight="1"/>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="183">
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="U52:X52"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="A58:T58"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="U54:X54"/>
+    <mergeCell ref="M57:P57"/>
+    <mergeCell ref="M14:P14"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="M46:P46"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="Q55:R55"/>
+    <mergeCell ref="M56:P56"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="U15:X15"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="S57:T57"/>
+    <mergeCell ref="Q62:T62"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="K62:P62"/>
+    <mergeCell ref="C20:L20"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="A67:X67"/>
+    <mergeCell ref="Q63:T63"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="U57:X57"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="M16:P16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="C46:L46"/>
+    <mergeCell ref="A28:T28"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="M45:P45"/>
+    <mergeCell ref="Q53:R53"/>
+    <mergeCell ref="S47:T47"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="A48:T48"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="S46:T46"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="Q52:R52"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="S52:T52"/>
+    <mergeCell ref="U14:X14"/>
+    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="Q54:R54"/>
+    <mergeCell ref="A50:X50"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="A42:X42"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="M44:P44"/>
+    <mergeCell ref="U46:X46"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="U48:X48"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="C16:L16"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C55:L55"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="U47:X47"/>
+    <mergeCell ref="A64:X64"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="U56:X56"/>
+    <mergeCell ref="Q57:R57"/>
+    <mergeCell ref="A61:X61"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="U58:X58"/>
+    <mergeCell ref="K63:P63"/>
+    <mergeCell ref="C52:L52"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="M53:P53"/>
+    <mergeCell ref="U44:X44"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="M55:P55"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="U45:X45"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="Q46:R46"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C54:L54"/>
+    <mergeCell ref="S55:T55"/>
+    <mergeCell ref="Q45:R45"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="C56:L56"/>
+    <mergeCell ref="S54:T54"/>
+    <mergeCell ref="A11:X11"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="Q47:R47"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="U62:X62"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q56:R56"/>
+    <mergeCell ref="S56:T56"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="C17:L17"/>
+    <mergeCell ref="U55:X55"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="U63:X63"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="M52:P52"/>
+    <mergeCell ref="C45:L45"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="C47:L47"/>
+    <mergeCell ref="S45:T45"/>
+    <mergeCell ref="C44:L44"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="U53:X53"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C21:L21"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="M15:P15"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q45 Q46 Q47 Q53 Q54 Q55 Q56 Q57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S45 S46 S47 S53 S54 S55 S56 S57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"UA"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/geomcheuk-budae.xlsx
+++ b/web/public/forms/geomcheuk-budae.xlsx
@@ -601,7 +601,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="21" t="inlineStr">

--- a/web/public/forms/geomcheuk-budae.xlsx
+++ b/web/public/forms/geomcheuk-budae.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부대공 검측 체크리스트" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'부대공 검측 체크리스트'!$A$1:$X$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -200,9 +198,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1329,10 +1324,7 @@
       <c r="R28" s="5" t="n"/>
       <c r="S28" s="5" t="n"/>
       <c r="T28" s="5" t="n"/>
-      <c r="U28" s="13">
-        <f>IF(COUNTA(Q14:Q27,S14:S27)=0,"","합격 "&amp;COUNTA(Q14:Q27)&amp;" · 불합격 "&amp;COUNTA(S14:S27))</f>
-        <v/>
-      </c>
+      <c r="U28" s="13" t="n"/>
       <c r="V28" s="5" t="n"/>
       <c r="W28" s="5" t="n"/>
       <c r="X28" s="5" t="n"/>
@@ -1535,10 +1527,7 @@
       <c r="R48" s="5" t="n"/>
       <c r="S48" s="5" t="n"/>
       <c r="T48" s="5" t="n"/>
-      <c r="U48" s="13">
-        <f>IF(COUNTA(Q45:Q47,S45:S47)=0,"","합격 "&amp;COUNTA(Q45:Q47)&amp;" · 불합격 "&amp;COUNTA(S45:S47))</f>
-        <v/>
-      </c>
+      <c r="U48" s="13" t="n"/>
       <c r="V48" s="5" t="n"/>
       <c r="W48" s="5" t="n"/>
       <c r="X48" s="5" t="n"/>
@@ -1797,10 +1786,7 @@
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5" t="n"/>
       <c r="T58" s="5" t="n"/>
-      <c r="U58" s="13">
-        <f>IF(COUNTA(Q53:Q57,S53:S57)=0,"","합격 "&amp;COUNTA(Q53:Q57)&amp;" · 불합격 "&amp;COUNTA(S53:S57))</f>
-        <v/>
-      </c>
+      <c r="U58" s="13" t="n"/>
       <c r="V58" s="5" t="n"/>
       <c r="W58" s="5" t="n"/>
       <c r="X58" s="5" t="n"/>
@@ -1850,6 +1836,7 @@
       </c>
     </row>
     <row r="65" ht="6" customHeight="1"/>
+    <row r="66"/>
     <row r="67" ht="34" customHeight="1">
       <c r="A67" s="20" t="inlineStr">
         <is>
@@ -2071,1611 +2058,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X67"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>검 측 체 크 리 스 트  (부대공)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공        종</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>부대공 — 방음벽</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  위치 및 부위</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>STA.0+500 ~ 0+560 좌측</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  검 측 일 자</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="7" t="n">
-        <v>46294</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공  사  량</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>L=60m</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>▣ 방음벽(방음판)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="6" customHeight="1"/>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>검사 항목</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>검사기준</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="9" t="inlineStr">
-        <is>
-          <t>조치사항</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>기초지반의 잡석은 다져저 있는지 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="10" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="10" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="10" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>기초부의 폭, 연장, 선형은 도면과 일치하는가?</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="10" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="10" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="10" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>도수로 시공부위의 배수관 시설 설치위치는 도면과 일치하는가?</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="10" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="10" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="10" t="n"/>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>거푸집은 견고하고 단차나 틈, 철근조립 상태는 도면과 일치하는가?</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="10" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="10" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="10" t="n"/>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>지주간격이 방음판 규격에 맞추어 일정간격이 유지되도록 배치되었는가?</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="10" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="10" t="n"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>지주의 높이가 도면대로 시공되었는가?</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>방음벽 구체 콘크리트의 상단면은 틈새가 생기지 않도록 평활하게 마무리되었는가?</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="10" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="10" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>콘크리트 타설면의 미관은 양호하며 선형은 도면과 일치하는가?</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="10" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="10" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="10" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>방음판 하단부 틈새 발생은 없는가?</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="10" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="10" t="n"/>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="10" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>방음판의 재질 및 구조가 시방기준에 적합한가?</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="10" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="10" t="n"/>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="10" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>운반 및 보관중 손상된 것을 설치하지 않는가?</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="10" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="10" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="10" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>방음판에 내장된 흡음재의 열화 및 처짐방지용 보호피막이 도포되어 있는가?</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="10" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="10" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="10" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>설치기준에 부합되는가?</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="10" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="10" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="10" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>선정기준에 부합되는가?</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="10" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="10" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>결  과</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n"/>
-      <c r="T28" s="5" t="n"/>
-      <c r="U28" s="13">
-        <f>IF(COUNTA(Q14:Q27,S14:S27)=0,"","합격 "&amp;COUNTA(Q14:Q27)&amp;" · 불합격 "&amp;COUNTA(S14:S27))</f>
-        <v/>
-      </c>
-      <c r="V28" s="5" t="n"/>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="7.666666666666667" customHeight="1"/>
-    <row r="31" ht="7.666666666666667" customHeight="1"/>
-    <row r="32" ht="7.666666666666667" customHeight="1"/>
-    <row r="33" ht="7.666666666666667" customHeight="1"/>
-    <row r="34" ht="7.666666666666667" customHeight="1"/>
-    <row r="35" ht="7.666666666666667" customHeight="1"/>
-    <row r="36" ht="7.666666666666667" customHeight="1"/>
-    <row r="37" ht="7.666666666666667" customHeight="1"/>
-    <row r="38" ht="7.666666666666667" customHeight="1"/>
-    <row r="39" ht="7.666666666666667" customHeight="1"/>
-    <row r="40" ht="7.666666666666667" customHeight="1"/>
-    <row r="41" ht="7.666666666666667" customHeight="1"/>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>▣ 방음벽(기초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="6" customHeight="1"/>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>검사 항목</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>검사기준</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="n"/>
-      <c r="O44" s="5" t="n"/>
-      <c r="P44" s="5" t="n"/>
-      <c r="Q44" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="R44" s="5" t="n"/>
-      <c r="S44" s="9" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="T44" s="5" t="n"/>
-      <c r="U44" s="9" t="inlineStr">
-        <is>
-          <t>조치사항</t>
-        </is>
-      </c>
-      <c r="V44" s="5" t="n"/>
-      <c r="W44" s="5" t="n"/>
-      <c r="X44" s="5" t="n"/>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>기초의 폭,연장, 선형 및 지지력은 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="10" t="n"/>
-      <c r="N45" s="5" t="n"/>
-      <c r="O45" s="5" t="n"/>
-      <c r="P45" s="5" t="n"/>
-      <c r="Q45" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R45" s="5" t="n"/>
-      <c r="S45" s="10" t="n"/>
-      <c r="T45" s="5" t="n"/>
-      <c r="U45" s="10" t="n"/>
-      <c r="V45" s="5" t="n"/>
-      <c r="W45" s="5" t="n"/>
-      <c r="X45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>도수로 시공부위의 배수관, 집수정 시설 설치위치는 적정한가?</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="5" t="n"/>
-      <c r="O46" s="5" t="n"/>
-      <c r="P46" s="5" t="n"/>
-      <c r="Q46" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R46" s="5" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="5" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="5" t="n"/>
-      <c r="W46" s="5" t="n"/>
-      <c r="X46" s="5" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>거푸집 설치 및 철근조립 상태는 양호한가?</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="10" t="n"/>
-      <c r="N47" s="5" t="n"/>
-      <c r="O47" s="5" t="n"/>
-      <c r="P47" s="5" t="n"/>
-      <c r="Q47" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R47" s="5" t="n"/>
-      <c r="S47" s="10" t="n"/>
-      <c r="T47" s="5" t="n"/>
-      <c r="U47" s="10" t="n"/>
-      <c r="V47" s="5" t="n"/>
-      <c r="W47" s="5" t="n"/>
-      <c r="X47" s="5" t="n"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>결  과</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="n"/>
-      <c r="O48" s="5" t="n"/>
-      <c r="P48" s="5" t="n"/>
-      <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
-      <c r="S48" s="5" t="n"/>
-      <c r="T48" s="5" t="n"/>
-      <c r="U48" s="13">
-        <f>IF(COUNTA(Q45:Q47,S45:S47)=0,"","합격 "&amp;COUNTA(Q45:Q47)&amp;" · 불합격 "&amp;COUNTA(S45:S47))</f>
-        <v/>
-      </c>
-      <c r="V48" s="5" t="n"/>
-      <c r="W48" s="5" t="n"/>
-      <c r="X48" s="5" t="n"/>
-    </row>
-    <row r="49" ht="6" customHeight="1"/>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>▣ 방음벽(구체)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="6" customHeight="1"/>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>검사 항목</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="9" t="inlineStr">
-        <is>
-          <t>검사기준</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="n"/>
-      <c r="O52" s="5" t="n"/>
-      <c r="P52" s="5" t="n"/>
-      <c r="Q52" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="R52" s="5" t="n"/>
-      <c r="S52" s="9" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="T52" s="5" t="n"/>
-      <c r="U52" s="9" t="inlineStr">
-        <is>
-          <t>조치사항</t>
-        </is>
-      </c>
-      <c r="V52" s="5" t="n"/>
-      <c r="W52" s="5" t="n"/>
-      <c r="X52" s="5" t="n"/>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>지주간격이 방음판 규격에 맟추어 일정간격이 유지되도록 배치되었는가?</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="10" t="n"/>
-      <c r="N53" s="5" t="n"/>
-      <c r="O53" s="5" t="n"/>
-      <c r="P53" s="5" t="n"/>
-      <c r="Q53" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R53" s="5" t="n"/>
-      <c r="S53" s="10" t="n"/>
-      <c r="T53" s="5" t="n"/>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="5" t="n"/>
-      <c r="W53" s="5" t="n"/>
-      <c r="X53" s="5" t="n"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>지주의 높이가 설계대로 시공되었는가?</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="10" t="n"/>
-      <c r="N54" s="5" t="n"/>
-      <c r="O54" s="5" t="n"/>
-      <c r="P54" s="5" t="n"/>
-      <c r="Q54" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R54" s="5" t="n"/>
-      <c r="S54" s="10" t="n"/>
-      <c r="T54" s="5" t="n"/>
-      <c r="U54" s="10" t="n"/>
-      <c r="V54" s="5" t="n"/>
-      <c r="W54" s="5" t="n"/>
-      <c r="X54" s="5" t="n"/>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>방음벽 구체 콘크리트의 상단면은 틈새가 생기지 않도록 평활하게 마무리 되었는가?</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="10" t="n"/>
-      <c r="N55" s="5" t="n"/>
-      <c r="O55" s="5" t="n"/>
-      <c r="P55" s="5" t="n"/>
-      <c r="Q55" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R55" s="5" t="n"/>
-      <c r="S55" s="10" t="n"/>
-      <c r="T55" s="5" t="n"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="5" t="n"/>
-      <c r="W55" s="5" t="n"/>
-      <c r="X55" s="5" t="n"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>거푸집 설치및철근 조립상태는 양호한가?</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="10" t="n"/>
-      <c r="N56" s="5" t="n"/>
-      <c r="O56" s="5" t="n"/>
-      <c r="P56" s="5" t="n"/>
-      <c r="Q56" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R56" s="5" t="n"/>
-      <c r="S56" s="10" t="n"/>
-      <c r="T56" s="5" t="n"/>
-      <c r="U56" s="10" t="n"/>
-      <c r="V56" s="5" t="n"/>
-      <c r="W56" s="5" t="n"/>
-      <c r="X56" s="5" t="n"/>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>콘크리트 타설면의 미관 및 선형은 양호한가?</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="10" t="n"/>
-      <c r="N57" s="5" t="n"/>
-      <c r="O57" s="5" t="n"/>
-      <c r="P57" s="5" t="n"/>
-      <c r="Q57" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R57" s="5" t="n"/>
-      <c r="S57" s="10" t="n"/>
-      <c r="T57" s="5" t="n"/>
-      <c r="U57" s="10" t="n"/>
-      <c r="V57" s="5" t="n"/>
-      <c r="W57" s="5" t="n"/>
-      <c r="X57" s="5" t="n"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>결  과</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="n"/>
-      <c r="O58" s="5" t="n"/>
-      <c r="P58" s="5" t="n"/>
-      <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="5" t="n"/>
-      <c r="S58" s="5" t="n"/>
-      <c r="T58" s="5" t="n"/>
-      <c r="U58" s="13">
-        <f>IF(COUNTA(Q53:Q57,S53:S57)=0,"","합격 "&amp;COUNTA(Q53:Q57)&amp;" · 불합격 "&amp;COUNTA(S53:S57))</f>
-        <v/>
-      </c>
-      <c r="V58" s="5" t="n"/>
-      <c r="W58" s="5" t="n"/>
-      <c r="X58" s="5" t="n"/>
-    </row>
-    <row r="59" ht="6" customHeight="1"/>
-    <row r="60" ht="10" customHeight="1"/>
-    <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="14" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="15" t="inlineStr"/>
-      <c r="K62" s="16" t="inlineStr">
-        <is>
-          <t>시공자 점검직원</t>
-        </is>
-      </c>
-      <c r="Q62" s="17" t="inlineStr">
-        <is>
-          <t>이감독</t>
-        </is>
-      </c>
-      <c r="U62" s="18" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="15" t="inlineStr"/>
-      <c r="K63" s="16" t="inlineStr">
-        <is>
-          <t>검측 감리원</t>
-        </is>
-      </c>
-      <c r="Q63" s="17" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="U63" s="18" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="19" t="inlineStr">
-        <is>
-          <t>※ 검사·시험값이 있으면 값을 적고, 합격은 A · 불합격은 UA 로 표기합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="6" customHeight="1"/>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="20" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="183">
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="U52:X52"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="A58:T58"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="U54:X54"/>
-    <mergeCell ref="M57:P57"/>
-    <mergeCell ref="M14:P14"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="A63:J63"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="M46:P46"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="Q55:R55"/>
-    <mergeCell ref="M56:P56"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="U15:X15"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="S57:T57"/>
-    <mergeCell ref="Q62:T62"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="K62:P62"/>
-    <mergeCell ref="C20:L20"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M54:P54"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="A67:X67"/>
-    <mergeCell ref="Q63:T63"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="U57:X57"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="M16:P16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="C46:L46"/>
-    <mergeCell ref="A28:T28"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="M45:P45"/>
-    <mergeCell ref="Q53:R53"/>
-    <mergeCell ref="S47:T47"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="A48:T48"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="S46:T46"/>
-    <mergeCell ref="M47:P47"/>
-    <mergeCell ref="Q52:R52"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="S52:T52"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="M19:P19"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="Q54:R54"/>
-    <mergeCell ref="A50:X50"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="A42:X42"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="M44:P44"/>
-    <mergeCell ref="U46:X46"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="U48:X48"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="C16:L16"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C55:L55"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="U47:X47"/>
-    <mergeCell ref="A64:X64"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="U56:X56"/>
-    <mergeCell ref="Q57:R57"/>
-    <mergeCell ref="A61:X61"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="M27:P27"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="U58:X58"/>
-    <mergeCell ref="K63:P63"/>
-    <mergeCell ref="C52:L52"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="M53:P53"/>
-    <mergeCell ref="U44:X44"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="M55:P55"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="U45:X45"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="S53:T53"/>
-    <mergeCell ref="Q46:R46"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C54:L54"/>
-    <mergeCell ref="S55:T55"/>
-    <mergeCell ref="Q45:R45"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="C56:L56"/>
-    <mergeCell ref="S54:T54"/>
-    <mergeCell ref="A11:X11"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="Q47:R47"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="U62:X62"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q56:R56"/>
-    <mergeCell ref="S56:T56"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="C17:L17"/>
-    <mergeCell ref="U55:X55"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="U26:X26"/>
-    <mergeCell ref="C53:L53"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="U63:X63"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="M52:P52"/>
-    <mergeCell ref="C45:L45"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="C47:L47"/>
-    <mergeCell ref="S45:T45"/>
-    <mergeCell ref="C44:L44"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="U53:X53"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C21:L21"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="M15:P15"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q45 Q46 Q47 Q53 Q54 Q55 Q56 Q57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S45 S46 S47 S53 S54 S55 S56 S57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"UA"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/geomcheuk-budae.xlsx
+++ b/web/public/forms/geomcheuk-budae.xlsx
@@ -596,7 +596,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
